--- a/timepass/scriptopedia/data/help.xlsx
+++ b/timepass/scriptopedia/data/help.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piklu\Documents\GitHub\projects.github.io\timepass\scriptopedia\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38559870-F857-4733-B26C-5132F0A816FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC64F9BA-C4A9-4EAB-B846-D61AE9AF5453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{8B40A149-55C4-4FF0-863D-D8CE9F770AA2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>HELP-FOR-SEARCH</t>
   </si>
@@ -183,6 +183,25 @@
         <family val="2"/>
       </rPr>
       <t>full form</t>
+    </r>
+  </si>
+  <si>
+    <t>How to build SQL queries</t>
+  </si>
+  <si>
+    <r>
+      <t>Type </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFAA205C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SQL query build</t>
     </r>
   </si>
 </sst>
@@ -456,6 +475,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -463,18 +494,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -799,20 +818,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="8.88671875" style="12"/>
     <col min="2" max="2" width="26.44140625" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -826,7 +845,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="56.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -837,7 +856,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -848,7 +867,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -858,15 +877,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14">
+    <row r="6" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
